--- a/2025_10_06_LACV_50N_no_NSs_exp1/data/2025_10_09_LACV_50N_no_NSs_exp1_tidy_template.xlsx
+++ b/2025_10_06_LACV_50N_no_NSs_exp1/data/2025_10_09_LACV_50N_no_NSs_exp1_tidy_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/charligeer/Documents/Lab_Projects/Repos/Bunya-50-N-experiments-update/2025_10_06_LACV_50N_no_NSs_exp1/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/charligeer/Documents/Lab_Projects/Repos/Bunya-50-N-experiments/2025_10_06_LACV_50N_no_NSs_exp1/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C62218CE-259B-2D48-9D3C-60BC016F4303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{306D3BC7-4D96-AD49-B97D-56C80E2268CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="26220" windowHeight="17300" xr2:uid="{CD6AA7B1-C22D-8C4D-94EB-7BEC7C6477A9}"/>
   </bookViews>
@@ -209,9 +209,6 @@
     <t>LACV with NSs</t>
   </si>
   <si>
-    <t>Trvittatus</t>
-  </si>
-  <si>
     <t>Jamestown Canyon</t>
   </si>
   <si>
@@ -225,6 +222,9 @@
   </si>
   <si>
     <t>Ilesha strain R5964</t>
+  </si>
+  <si>
+    <t>Trivittatus</t>
   </si>
 </sst>
 </file>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E34" s="1">
         <v>336</v>
@@ -1411,7 +1411,7 @@
         <v>9</v>
       </c>
       <c r="D35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E35" s="1">
         <v>337</v>
@@ -1455,7 +1455,7 @@
         <v>9</v>
       </c>
       <c r="D37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E37" s="1">
         <v>339</v>
@@ -1719,7 +1719,7 @@
         <v>9</v>
       </c>
       <c r="D49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E49" s="1">
         <v>351</v>
@@ -1741,7 +1741,7 @@
         <v>9</v>
       </c>
       <c r="D50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E50" s="1">
         <v>352</v>
@@ -1829,7 +1829,7 @@
         <v>9</v>
       </c>
       <c r="D54" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E54" s="1">
         <v>356</v>
@@ -2577,7 +2577,7 @@
         <v>9</v>
       </c>
       <c r="D88" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E88" s="1">
         <v>336</v>
@@ -2599,7 +2599,7 @@
         <v>9</v>
       </c>
       <c r="D89" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E89" s="1">
         <v>337</v>
@@ -2643,7 +2643,7 @@
         <v>9</v>
       </c>
       <c r="D91" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E91" s="1">
         <v>339</v>
@@ -2907,7 +2907,7 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E103" s="1">
         <v>351</v>
@@ -2929,7 +2929,7 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E104" s="1">
         <v>352</v>
@@ -3017,7 +3017,7 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E108" s="1">
         <v>356</v>
@@ -3765,7 +3765,7 @@
         <v>9</v>
       </c>
       <c r="D142" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E142" s="1">
         <v>336</v>
@@ -3787,7 +3787,7 @@
         <v>9</v>
       </c>
       <c r="D143" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E143" s="1">
         <v>337</v>
@@ -3831,7 +3831,7 @@
         <v>9</v>
       </c>
       <c r="D145" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E145" s="1">
         <v>339</v>
@@ -4095,7 +4095,7 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E157" s="1">
         <v>351</v>
@@ -4117,7 +4117,7 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E158" s="1">
         <v>352</v>
@@ -4205,7 +4205,7 @@
         <v>9</v>
       </c>
       <c r="D162" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E162" s="1">
         <v>356</v>
